--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-12 / 2026-09-12</t>
+          <t>Ventas 2026-09-13 / 2026-09-13</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3780.45</v>
+        <v>3351.5</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>416</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7518.18</v>
+        <v>6366.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>863</v>
+        <v>771</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2660.5</v>
+        <v>2315.18</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>351</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1125.05</v>
+        <v>842.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4356.32</v>
+        <v>3922.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>499</v>
+        <v>441</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3735.75</v>
+        <v>3139.77</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>488</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1640.63</v>
+        <v>1135.55</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>205</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3873.45</v>
+        <v>3794.85</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>414</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5960.1</v>
+        <v>4543.42</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>759</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-13 / 2026-09-13</t>
+          <t>Ventas 2026-09-14 / 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3351.5</v>
+        <v>2118.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>392</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6366.64</v>
+        <v>4783</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>771</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2315.18</v>
+        <v>1418.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>306</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>842.91</v>
+        <v>341.87</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3922.55</v>
+        <v>2336</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>441</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3139.77</v>
+        <v>2839.72</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>437</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1135.55</v>
+        <v>680.1799999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>144</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3794.85</v>
+        <v>3434.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>424</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4543.42</v>
+        <v>3087.34</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>597</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-14 / 2026-09-14</t>
+          <t>Ventas 2026-09-19 / 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2118.73</v>
+        <v>4172.64</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>251</v>
+        <v>453</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4783</v>
+        <v>7025.35</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>596</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1418.5</v>
+        <v>2289.41</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>196</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>341.87</v>
+        <v>1308.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2336</v>
+        <v>4653.25</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>294</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2839.72</v>
+        <v>3731.42</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>379</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>680.1799999999999</v>
+        <v>1626.69</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>95</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3434.45</v>
+        <v>4588.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>369</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3087.34</v>
+        <v>5932.11</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>421</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-19 / 2026-09-19</t>
+          <t>Ventas 2026-09-20 / 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4172.64</v>
+        <v>4362.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>453</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7025.35</v>
+        <v>6507.74</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>815</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2289.41</v>
+        <v>2237.59</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>287</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1308.36</v>
+        <v>736.73</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>190</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4653.25</v>
+        <v>3946.23</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>527</v>
+        <v>445</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3731.42</v>
+        <v>3387.77</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1626.69</v>
+        <v>1127.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>214</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4588.36</v>
+        <v>4895.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>501</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5932.11</v>
+        <v>4491.93</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>745</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-20 / 2026-09-20</t>
+          <t>Ventas 2026-09-18 / 2026-09-18</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4362.36</v>
+        <v>4094.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>478</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6507.74</v>
+        <v>5433.28</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>786</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2237.59</v>
+        <v>1930.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>303</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>736.73</v>
+        <v>403.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3946.23</v>
+        <v>2914.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>445</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3387.77</v>
+        <v>3453.45</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1127.32</v>
+        <v>840.5</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4895.45</v>
+        <v>2991.95</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>517</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4491.93</v>
+        <v>4679.36</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>588</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-18 / 2026-09-18</t>
+          <t>Ventas 2026-09-21 / 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4094.14</v>
+        <v>2997.74</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>456</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5433.28</v>
+        <v>4856.53</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>678</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1930.82</v>
+        <v>1712.05</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>266</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>403.91</v>
+        <v>511.82</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2914.45</v>
+        <v>2555</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>357</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3453.45</v>
+        <v>2296.64</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>445</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>840.5</v>
+        <v>661.45</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>2991.95</v>
+        <v>3811.82</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>310</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4679.36</v>
+        <v>3408.87</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>581</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-21 / 2026-09-21</t>
+          <t>Ventas 2026-09-22 / 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2997.74</v>
+        <v>2712.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>344</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4856.53</v>
+        <v>4628.28</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1712.05</v>
+        <v>1461.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>511.82</v>
+        <v>374.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2555</v>
+        <v>2192.06</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>329</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2296.64</v>
+        <v>2310.92</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>661.45</v>
+        <v>755.91</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3811.82</v>
+        <v>3935.91</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>417</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3408.87</v>
+        <v>3410.39</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-22 / 2026-09-22</t>
+          <t>Ventas 2026-09-23 / 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2712.73</v>
+        <v>2951.32</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4628.28</v>
+        <v>5222.55</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>599</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1461.82</v>
+        <v>1589.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>374.18</v>
+        <v>566.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2192.06</v>
+        <v>2295.27</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2310.92</v>
+        <v>2516.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>755.91</v>
+        <v>385.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3935.91</v>
+        <v>3752.27</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>452</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3410.39</v>
+        <v>2809.75</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>470</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-23 / 2026-09-23</t>
+          <t>Ventas 2026-09-24 / 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2951.32</v>
+        <v>2292.82</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5222.55</v>
+        <v>6478.64</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>677</v>
+        <v>814</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1589.23</v>
+        <v>3242.95</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>566.64</v>
+        <v>546.91</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2295.27</v>
+        <v>2953.86</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>292</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2516.91</v>
+        <v>2721.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>336</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>385.05</v>
+        <v>610.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3752.27</v>
+        <v>3581</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>429</v>
+        <v>406</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2809.75</v>
+        <v>3259.18</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>373</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-24 / 2026-09-24</t>
+          <t>Ventas 2026-09-25 / 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2292.82</v>
+        <v>2592.01</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>268</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6478.64</v>
+        <v>6052.49</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>814</v>
+        <v>759</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3242.95</v>
+        <v>2223.68</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>546.91</v>
+        <v>583.8200000000001</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2953.86</v>
+        <v>3910.27</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>375</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2721.73</v>
+        <v>3430.02</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>393</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>610.41</v>
+        <v>772.91</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3581</v>
+        <v>4130.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>406</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3259.18</v>
+        <v>4420.45</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>435</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-25 / 2026-09-25</t>
+          <t>Ventas 2026-09-26 / 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2592.01</v>
+        <v>4225.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6052.49</v>
+        <v>7331.45</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>759</v>
+        <v>851</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2223.68</v>
+        <v>2817</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>583.8200000000001</v>
+        <v>1154.59</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3910.27</v>
+        <v>4097.41</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>460</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3430.02</v>
+        <v>4011.68</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>772.91</v>
+        <v>1202.95</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4130.45</v>
+        <v>5289</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>451</v>
+        <v>586</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4420.45</v>
+        <v>5641.7</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>575</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-26 / 2026-09-26</t>
+          <t>Ventas 2026-09-27 / 2026-09-27</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4225.23</v>
+        <v>3587.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>459</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7331.45</v>
+        <v>6145.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>851</v>
+        <v>723</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2817</v>
+        <v>3008.77</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1154.59</v>
+        <v>1152.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4097.41</v>
+        <v>3282.09</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>491</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4011.68</v>
+        <v>3057.97</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>522</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1202.95</v>
+        <v>1128.6</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>5289</v>
+        <v>4647.77</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>586</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5641.7</v>
+        <v>4291.88</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>678</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-27 / 2026-09-27</t>
+          <t>Ventas 2026-09-28 / 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3587.41</v>
+        <v>2259.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>392</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6145.59</v>
+        <v>4372.68</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>723</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3008.77</v>
+        <v>1623.36</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1152.18</v>
+        <v>202.82</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>159</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3282.09</v>
+        <v>930</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>388</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3057.97</v>
+        <v>2083.95</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>417</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1128.6</v>
+        <v>536</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>151</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4647.77</v>
+        <v>4003.59</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>489</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4291.88</v>
+        <v>3144.45</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>538</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-28 / 2026-09-28</t>
+          <t>Ventas 2026-09-29 / 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2259.55</v>
+        <v>2088</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4372.68</v>
+        <v>4029.91</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>539</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1623.36</v>
+        <v>1401.32</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>202.82</v>
+        <v>402.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>930</v>
+        <v>1551.36</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2083.95</v>
+        <v>2373.14</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>282</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>525.13</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4003.59</v>
+        <v>3630</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>440</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3144.45</v>
+        <v>2738.37</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>416</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-29 / 2026-09-29</t>
+          <t>Ventas 2026-09-30 / 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4029.91</v>
+        <v>4282.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>499</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1401.32</v>
+        <v>1426.59</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>402.36</v>
+        <v>314.82</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1551.36</v>
+        <v>1460.27</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2373.14</v>
+        <v>2108.33</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>346</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -547,7 +547,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>525.13</v>
+        <v>520.1900000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3630</v>
+        <v>3550.27</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>397</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2738.37</v>
+        <v>2616.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>368</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-09-30 / 2026-09-30</t>
+          <t>Ventas 2026-10-01 / 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2094</v>
+        <v>2226.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4282.09</v>
+        <v>4081.42</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1426.59</v>
+        <v>1528.36</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>314.82</v>
+        <v>532.9299999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1460.27</v>
+        <v>1897.95</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2108.33</v>
+        <v>2193.45</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>520.1900000000001</v>
+        <v>632.51</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3550.27</v>
+        <v>3896.14</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>383</v>
+        <v>433</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2616.35</v>
+        <v>2096.72</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>345</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-01 / 2026-10-01</t>
+          <t>Ventas 2026-10-02 / 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2226.23</v>
+        <v>1473.75</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>265</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4081.42</v>
+        <v>4597.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>540</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1528.36</v>
+        <v>1655.77</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>532.9299999999999</v>
+        <v>582.05</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1897.95</v>
+        <v>1491.18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2193.45</v>
+        <v>3185.77</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>302</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>632.51</v>
+        <v>854.3200000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3896.14</v>
+        <v>4394</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>433</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2096.72</v>
+        <v>3180.65</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>265</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-02 / 2026-10-02</t>
+          <t>Ventas 2026-10-03 / 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1473.75</v>
+        <v>4084.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>175</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4597.27</v>
+        <v>2049.75</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>575</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1655.77</v>
+        <v>615.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>582.05</v>
+        <v>800.95</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1491.18</v>
+        <v>2170.23</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>195</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3185.77</v>
+        <v>3215.36</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>410</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>854.3200000000001</v>
+        <v>1309.51</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4394</v>
+        <v>5381.76</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>490</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3180.65</v>
+        <v>5504.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>419</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-03 / 2026-10-03</t>
+          <t>Ventas 2026-10-04 / 2026-10-04</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4084.45</v>
+        <v>4084.41</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2049.75</v>
+        <v>2473.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>252</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>615.45</v>
+        <v>2757.75</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>800.95</v>
+        <v>460.32</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2170.23</v>
+        <v>1958.77</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3215.36</v>
+        <v>2917.57</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>432</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1309.51</v>
+        <v>732.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>180</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>5381.76</v>
+        <v>5395.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>559</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5504.35</v>
+        <v>4827.24</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>658</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-04 / 2026-10-04</t>
+          <t>Ventas 2026-10-05 / 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4084.41</v>
+        <v>2374.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>426</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2473.09</v>
+        <v>3531.86</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>280</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2757.75</v>
+        <v>1415.68</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>460.32</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1958.77</v>
+        <v>1369.36</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>227</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2917.57</v>
+        <v>1797.5</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>362</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>732.36</v>
+        <v>403.91</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>108</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>5395.45</v>
+        <v>3303.88</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>572</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4827.24</v>
+        <v>2605.3</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>599</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-05 / 2026-10-05</t>
+          <t>Ventas 2026-10-06 / 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2374.36</v>
+        <v>2916.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3531.86</v>
+        <v>2196.27</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>467</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1415.68</v>
+        <v>863.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>181</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>285.09</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1369.36</v>
+        <v>731.61</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>174</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1797.5</v>
+        <v>2668.87</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>250</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>403.91</v>
+        <v>702.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3303.88</v>
+        <v>3668.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2605.3</v>
+        <v>2688.75</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>346</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-06 / 2026-10-06</t>
+          <t>Ventas 2026-10-07 / 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2916.95</v>
+        <v>2195.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>295</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2196.27</v>
+        <v>4490.15</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>296</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>863.09</v>
+        <v>1723.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>119</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>285.09</v>
+        <v>423.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>731.61</v>
+        <v>1148.91</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>101</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2668.87</v>
+        <v>2486.73</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>360</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>702.41</v>
+        <v>540.55</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3668.64</v>
+        <v>3752.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2688.75</v>
+        <v>2379.92</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>387</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-07 / 2026-10-07</t>
+          <t>Ventas 2026-10-08 / 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2195.36</v>
+        <v>2668.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>250</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4490.15</v>
+        <v>3188.82</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>579</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1723.82</v>
+        <v>1089.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>214</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>423.64</v>
+        <v>564.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1148.91</v>
+        <v>1087.91</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2486.73</v>
+        <v>2311.56</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>338</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>540.55</v>
+        <v>457.77</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3752.64</v>
+        <v>3783.41</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2379.92</v>
+        <v>2375.42</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-08 / 2026-10-08</t>
+          <t>Ventas 2026-10-09 / 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2668.68</v>
+        <v>4447.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>305</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3188.82</v>
+        <v>4888.14</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>401</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1089.09</v>
+        <v>1907.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>147</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>564.64</v>
+        <v>586.1799999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1087.91</v>
+        <v>1898</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2311.56</v>
+        <v>3311.82</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>304</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>457.77</v>
+        <v>708.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3783.41</v>
+        <v>4241.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>396</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2375.42</v>
+        <v>4090.56</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>335</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-09 / 2026-10-09</t>
+          <t>Ventas 2026-10-10 / 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4447.55</v>
+        <v>4531.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4888.14</v>
+        <v>2788.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>626</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1907.82</v>
+        <v>2523.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>234</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>586.1799999999999</v>
+        <v>1317.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1898</v>
+        <v>3217.18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3311.82</v>
+        <v>4095.25</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>410</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>708.36</v>
+        <v>1362.82</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>103</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4241.18</v>
+        <v>4142.91</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>425</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4090.56</v>
+        <v>5009.21</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>506</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-10 / 2026-10-10</t>
+          <t>Ventas 2026-10-11 / 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4531.68</v>
+        <v>4606.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>508</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2788.09</v>
+        <v>7199.59</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>319</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2523.23</v>
+        <v>3080.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>314</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1317.18</v>
+        <v>1569.27</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>146</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3217.18</v>
+        <v>3665.09</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>376</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4095.25</v>
+        <v>4203.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1362.82</v>
+        <v>980.23</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>179</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4142.91</v>
+        <v>5500.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>441</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5009.21</v>
+        <v>4983.05</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-11 / 2026-10-11</t>
+          <t>Ventas 2026-10-12 / 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>4606.55</v>
+        <v>3596.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>475</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>7199.59</v>
+        <v>6119.82</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>790</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3080.45</v>
+        <v>2247.6</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>395</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1569.27</v>
+        <v>1337.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>212</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>3665.09</v>
+        <v>2462.82</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>414</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4203.55</v>
+        <v>2999.94</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>479</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>980.23</v>
+        <v>1246.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>5500.55</v>
+        <v>4213.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>599</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4983.05</v>
+        <v>4003.94</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>641</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-12 / 2026-10-12</t>
+          <t>Ventas 2026-10-13 / 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3596.86</v>
+        <v>2606.77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>386</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>6119.82</v>
+        <v>4424.51</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>735</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2247.6</v>
+        <v>1688.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>288</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1337.45</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2462.82</v>
+        <v>1457.73</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>291</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2999.94</v>
+        <v>2413.1</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>366</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1246.32</v>
+        <v>609.14</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>162</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4213.45</v>
+        <v>4403.14</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>425</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4003.94</v>
+        <v>1998.37</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>486</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-13 / 2026-10-13</t>
+          <t>Ventas 2026-10-14 / 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2606.77</v>
+        <v>1856.73</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>278</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4424.51</v>
+        <v>4085.23</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>526</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1688.09</v>
+        <v>1718.85</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>613.1799999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1457.73</v>
+        <v>1575</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2413.1</v>
+        <v>2100.19</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>318</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>609.14</v>
+        <v>554.8200000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4403.14</v>
+        <v>4039.91</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>467</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1998.37</v>
+        <v>2378.33</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>260</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-14 / 2026-10-14</t>
+          <t>Ventas 2026-10-15 / 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1856.73</v>
+        <v>2308.59</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4085.23</v>
+        <v>4459.33</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>540</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1718.85</v>
+        <v>1559.86</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>235</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>613.1799999999999</v>
+        <v>918.1799999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1575</v>
+        <v>1590.47</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>209</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2100.19</v>
+        <v>2185.34</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>554.8200000000001</v>
+        <v>646.39</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4039.91</v>
+        <v>3713.23</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>422</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2378.33</v>
+        <v>2268.25</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-15 / 2026-10-15</t>
+          <t>Ventas 2026-10-16 / 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2308.59</v>
+        <v>2592.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>246</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4459.33</v>
+        <v>5408.31</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>552</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1559.86</v>
+        <v>2137.18</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>198</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>918.1799999999999</v>
+        <v>919.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1590.47</v>
+        <v>1890.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2185.34</v>
+        <v>3197.68</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>301</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>646.39</v>
+        <v>769.79</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3713.23</v>
+        <v>4530.95</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>383</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2268.25</v>
+        <v>3501.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>297</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-16 / 2026-10-16</t>
+          <t>Ventas 2026-10-18 / 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2592.55</v>
+        <v>2991.45</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>284</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5408.31</v>
+        <v>3726.14</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>666</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2137.18</v>
+        <v>2143.73</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>253</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>919.36</v>
+        <v>554</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1890.55</v>
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3197.68</v>
+        <v>3846.48</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>421</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>769.79</v>
+        <v>492.89</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4530.95</v>
+        <v>4627.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>474</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3501.35</v>
+        <v>1414.32</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>455</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-18 / 2026-10-18</t>
+          <t>Ventas 2026-10-19 / 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2991.45</v>
+        <v>2992.68</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3726.14</v>
+        <v>1902.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>459</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2143.73</v>
+        <v>1206.91</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>267</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1027.86</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3846.48</v>
+        <v>2364.41</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>471</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>492.89</v>
+        <v>689.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4627.55</v>
+        <v>4220.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>505</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1414.32</v>
+        <v>1746.73</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>160</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-19 / 2026-10-19</t>
+          <t>Ventas 2026-10-20 / 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2992.68</v>
+        <v>2370.64</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>330</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1902.36</v>
+        <v>3481.6</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>258</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1206.91</v>
+        <v>1720.32</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>266.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1027.86</v>
+        <v>1050.45</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2364.41</v>
+        <v>2093.36</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>689.09</v>
+        <v>525</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4220.55</v>
+        <v>4111.41</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>452</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1746.73</v>
+        <v>2397.72</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>236</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-20 / 2026-10-20</t>
+          <t>Ventas 2026-10-21 / 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2370.64</v>
+        <v>2690.59</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>254</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3481.6</v>
+        <v>3468.77</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1720.32</v>
+        <v>1548.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>266.36</v>
+        <v>407.27</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1050.45</v>
+        <v>1077.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2093.36</v>
+        <v>2201.45</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>277</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>525</v>
+        <v>546.6799999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4111.41</v>
+        <v>3765.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>414</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2397.72</v>
+        <v>2549.11</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>299</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-21 / 2026-10-21</t>
+          <t>Ventas 2026-10-22 / 2026-10-22</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2690.59</v>
+        <v>2569.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>324</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3468.77</v>
+        <v>3825.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1548.82</v>
+        <v>1384.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>407.27</v>
+        <v>407.41</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1077.55</v>
+        <v>1505.64</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>140</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2201.45</v>
+        <v>2137.19</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>546.6799999999999</v>
+        <v>609.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3765.18</v>
+        <v>4029.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>381</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2549.11</v>
+        <v>2655.66</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-22 / 2026-10-22</t>
+          <t>Ventas 2026-10-23 / 2026-10-23</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2569.23</v>
+        <v>2886.36</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>274</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3825.09</v>
+        <v>5090.91</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>467</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1384.82</v>
+        <v>2286.14</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>189</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>407.41</v>
+        <v>431.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1505.64</v>
+        <v>1517.18</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2137.19</v>
+        <v>2940.59</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>274</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>609.36</v>
+        <v>663.27</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4029.64</v>
+        <v>3905.18</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>434</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2655.66</v>
+        <v>3088.94</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>332</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-23 / 2026-10-23</t>
+          <t>Ventas 2026-10-24 / 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2886.36</v>
+        <v>3032.59</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5090.91</v>
+        <v>4693.36</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>615</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2286.14</v>
+        <v>1772.45</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>294</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>431.18</v>
+        <v>924.45</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1517.18</v>
+        <v>2055.59</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>195</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2940.59</v>
+        <v>3613.55</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>389</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>663.27</v>
+        <v>1267.32</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>87</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3905.18</v>
+        <v>3926.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>402</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3088.94</v>
+        <v>4287.06</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>387</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-24 / 2026-10-24</t>
+          <t>Ventas 2026-10-25 / 2026-10-25</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3032.59</v>
+        <v>3117.14</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>318</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4693.36</v>
+        <v>5427.73</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>530</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1772.45</v>
+        <v>2730.71</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>924.45</v>
+        <v>594.5</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2055.59</v>
+        <v>2377.36</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>248</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3613.55</v>
+        <v>3188.06</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>450</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1267.32</v>
+        <v>770.1799999999999</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>168</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3926.55</v>
+        <v>3985.14</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>416</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>4287.06</v>
+        <v>3990.86</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>528</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-25 / 2026-10-25</t>
+          <t>Ventas 2026-10-26 / 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3117.14</v>
+        <v>2525.95</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>347</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>5427.73</v>
+        <v>4779.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>627</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2730.71</v>
+        <v>1634.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>327</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>594.5</v>
+        <v>0</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>2377.36</v>
+        <v>1467.95</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>284</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3188.06</v>
+        <v>2092.62</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>399</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>770.1799999999999</v>
+        <v>709.05</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3985.14</v>
+        <v>4165.32</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3990.86</v>
+        <v>2551.55</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>492</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-26 / 2026-10-26</t>
+          <t>Ventas 2026-10-27 / 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2525.95</v>
+        <v>3220.55</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>264</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4779.09</v>
+        <v>4451.85</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1634.09</v>
+        <v>2109.82</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>203</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>255.64</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1467.95</v>
+        <v>1493.09</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>203</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2092.62</v>
+        <v>2743.94</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>266</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>709.05</v>
+        <v>594.09</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>4165.32</v>
+        <v>3681</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>401</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2551.55</v>
+        <v>1783.33</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>305</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-27 / 2026-10-27</t>
+          <t>Ventas 2026-10-28 / 2026-10-28</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>3220.55</v>
+        <v>2794.77</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>358</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4451.85</v>
+        <v>4173.09</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>539</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2109.82</v>
+        <v>1908.18</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>255.64</v>
+        <v>407.36</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1493.09</v>
+        <v>1113.55</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2743.94</v>
+        <v>2085.75</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>594.09</v>
+        <v>444.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3681</v>
+        <v>3296.59</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>356</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1783.33</v>
+        <v>2007.42</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-28 / 2026-10-28</t>
+          <t>Ventas 2026-10-29 / 2026-10-29</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2794.77</v>
+        <v>2513.23</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>301</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>4173.09</v>
+        <v>3815.11</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1908.18</v>
+        <v>1439.5</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>242</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>407.36</v>
+        <v>567.77</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1113.55</v>
+        <v>1645.14</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2085.75</v>
+        <v>2031.35</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>444.41</v>
+        <v>463.36</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3296.59</v>
+        <v>3604.09</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>332</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>2007.42</v>
+        <v>1988.66</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>

--- a/Ventas_ayer.xlsx
+++ b/Ventas_ayer.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2026-10-29 / 2026-10-29</t>
+          <t>Ventas 2026-10-30 / 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -451,12 +451,12 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>2513.23</v>
+        <v>2490.86</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4">
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>3815.11</v>
+        <v>4511.55</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>490</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1439.5</v>
+        <v>1514.09</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>567.77</v>
+        <v>614.55</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -515,12 +515,12 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1645.14</v>
+        <v>1937.64</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>190</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>2031.35</v>
+        <v>2817.23</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>266</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>463.36</v>
+        <v>724.3200000000001</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>3604.09</v>
+        <v>3281.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>367</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1988.66</v>
+        <v>2386.35</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>277</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
